--- a/data/nzd0109/nzd0109.xlsx
+++ b/data/nzd0109/nzd0109.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S320"/>
+  <dimension ref="A1:S322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20596,7 +20596,7 @@
         <v>398.54</v>
       </c>
       <c r="M320" t="n">
-        <v>399.27</v>
+        <v>404.95</v>
       </c>
       <c r="N320" t="n">
         <v>405.55</v>
@@ -20616,6 +20616,132 @@
       <c r="S320" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>382.2</v>
+      </c>
+      <c r="C321" t="n">
+        <v>383.42</v>
+      </c>
+      <c r="D321" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="E321" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="F321" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="G321" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="H321" t="n">
+        <v>385.29</v>
+      </c>
+      <c r="I321" t="n">
+        <v>390.93</v>
+      </c>
+      <c r="J321" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="K321" t="n">
+        <v>389.04</v>
+      </c>
+      <c r="L321" t="n">
+        <v>400.87</v>
+      </c>
+      <c r="M321" t="n">
+        <v>410.41</v>
+      </c>
+      <c r="N321" t="n">
+        <v>404.35</v>
+      </c>
+      <c r="O321" t="n">
+        <v>406.94</v>
+      </c>
+      <c r="P321" t="n">
+        <v>389.73</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="R321" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>383.19</v>
+      </c>
+      <c r="C322" t="n">
+        <v>383.85</v>
+      </c>
+      <c r="D322" t="n">
+        <v>383.11</v>
+      </c>
+      <c r="E322" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="F322" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="G322" t="n">
+        <v>379.57</v>
+      </c>
+      <c r="H322" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="I322" t="n">
+        <v>391.13</v>
+      </c>
+      <c r="J322" t="n">
+        <v>384.51</v>
+      </c>
+      <c r="K322" t="n">
+        <v>388.97</v>
+      </c>
+      <c r="L322" t="n">
+        <v>400.76</v>
+      </c>
+      <c r="M322" t="n">
+        <v>409.05</v>
+      </c>
+      <c r="N322" t="n">
+        <v>404.65</v>
+      </c>
+      <c r="O322" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="P322" t="n">
+        <v>390.01</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="R322" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B375"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24383,6 +24509,26 @@
       </c>
       <c r="B375" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -24551,28 +24697,28 @@
         <v>0.1305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1848102917078557</v>
+        <v>0.1726698191648065</v>
       </c>
       <c r="J2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07207995716266902</v>
+        <v>0.06303030223842454</v>
       </c>
       <c r="M2" t="n">
-        <v>3.786104438448871</v>
+        <v>3.82689417061169</v>
       </c>
       <c r="N2" t="n">
-        <v>23.45109318213402</v>
+        <v>23.84033214898674</v>
       </c>
       <c r="O2" t="n">
-        <v>4.842632877075653</v>
+        <v>4.882656259556548</v>
       </c>
       <c r="P2" t="n">
-        <v>387.1884535717845</v>
+        <v>387.3133580910885</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24629,28 +24775,28 @@
         <v>0.1047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3315084785213184</v>
+        <v>0.3131999119561787</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2201718471103372</v>
+        <v>0.1945462492096458</v>
       </c>
       <c r="M3" t="n">
-        <v>3.49899109677849</v>
+        <v>3.582648705681317</v>
       </c>
       <c r="N3" t="n">
-        <v>20.76065999811966</v>
+        <v>21.84561552893469</v>
       </c>
       <c r="O3" t="n">
-        <v>4.556386726137243</v>
+        <v>4.673929345736272</v>
       </c>
       <c r="P3" t="n">
-        <v>389.0252623203936</v>
+        <v>389.2136291044506</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24707,28 +24853,28 @@
         <v>0.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3415990551127382</v>
+        <v>0.3191723160433066</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1753627174101793</v>
+        <v>0.150598390635289</v>
       </c>
       <c r="M4" t="n">
-        <v>4.213711918972903</v>
+        <v>4.308506781887044</v>
       </c>
       <c r="N4" t="n">
-        <v>29.26670110470639</v>
+        <v>30.9062601649827</v>
       </c>
       <c r="O4" t="n">
-        <v>5.409870710535178</v>
+        <v>5.559339903710034</v>
       </c>
       <c r="P4" t="n">
-        <v>391.1786705473642</v>
+        <v>391.4094071488811</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24785,28 +24931,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3692650785527879</v>
+        <v>0.3471757228578917</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K5" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1754524429886807</v>
+        <v>0.1535719158202725</v>
       </c>
       <c r="M5" t="n">
-        <v>4.138643523040778</v>
+        <v>4.232625045298828</v>
       </c>
       <c r="N5" t="n">
-        <v>34.17806865924921</v>
+        <v>35.73388510578212</v>
       </c>
       <c r="O5" t="n">
-        <v>5.846201216110271</v>
+        <v>5.97778262450067</v>
       </c>
       <c r="P5" t="n">
-        <v>394.5147471291732</v>
+        <v>394.7420109234694</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24863,28 +25009,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3264035942096956</v>
+        <v>0.3144537235379742</v>
       </c>
       <c r="J6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L6" t="n">
-        <v>0.161165638714672</v>
+        <v>0.1509874496499088</v>
       </c>
       <c r="M6" t="n">
-        <v>4.17899678683486</v>
+        <v>4.217461112519191</v>
       </c>
       <c r="N6" t="n">
-        <v>29.57524663089795</v>
+        <v>29.90818245886509</v>
       </c>
       <c r="O6" t="n">
-        <v>5.438312847832308</v>
+        <v>5.468837395540764</v>
       </c>
       <c r="P6" t="n">
-        <v>384.630588613083</v>
+        <v>384.7535347032542</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24941,28 +25087,28 @@
         <v>0.0857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4061756815681052</v>
+        <v>0.3919220005002011</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2026048281442608</v>
+        <v>0.1903131083576485</v>
       </c>
       <c r="M7" t="n">
-        <v>4.512042376106262</v>
+        <v>4.551608202607867</v>
       </c>
       <c r="N7" t="n">
-        <v>34.63110894905851</v>
+        <v>35.15207527564811</v>
       </c>
       <c r="O7" t="n">
-        <v>5.884820213826291</v>
+        <v>5.928918558695853</v>
       </c>
       <c r="P7" t="n">
-        <v>379.489761081142</v>
+        <v>379.6364080812027</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25019,28 +25165,28 @@
         <v>0.1168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3765116028520663</v>
+        <v>0.3695210422174468</v>
       </c>
       <c r="J8" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K8" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L8" t="n">
-        <v>0.163184652020088</v>
+        <v>0.1594862465730915</v>
       </c>
       <c r="M8" t="n">
-        <v>4.722940606337255</v>
+        <v>4.72783574134077</v>
       </c>
       <c r="N8" t="n">
-        <v>38.77232169835191</v>
+        <v>38.70822106040094</v>
       </c>
       <c r="O8" t="n">
-        <v>6.226742462825318</v>
+        <v>6.221593128805591</v>
       </c>
       <c r="P8" t="n">
-        <v>381.0500262924263</v>
+        <v>381.1219471468447</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25097,28 +25243,28 @@
         <v>0.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4190256929547599</v>
+        <v>0.4133675917702815</v>
       </c>
       <c r="J9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2232842222157249</v>
+        <v>0.2205175680832676</v>
       </c>
       <c r="M9" t="n">
-        <v>4.452278739299924</v>
+        <v>4.453976355897998</v>
       </c>
       <c r="N9" t="n">
-        <v>32.57617946972668</v>
+        <v>32.48921842451829</v>
       </c>
       <c r="O9" t="n">
-        <v>5.707554596298372</v>
+        <v>5.6999314403349</v>
       </c>
       <c r="P9" t="n">
-        <v>384.3729845286725</v>
+        <v>384.4311974395648</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25175,28 +25321,28 @@
         <v>0.101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3786832595319003</v>
+        <v>0.3703324768849427</v>
       </c>
       <c r="J10" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K10" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1414174088383586</v>
+        <v>0.1371782508535999</v>
       </c>
       <c r="M10" t="n">
-        <v>5.177757916693656</v>
+        <v>5.184723624607617</v>
       </c>
       <c r="N10" t="n">
-        <v>46.43507676855602</v>
+        <v>46.40050422409453</v>
       </c>
       <c r="O10" t="n">
-        <v>6.814328783420714</v>
+        <v>6.811791557592946</v>
       </c>
       <c r="P10" t="n">
-        <v>380.3972957417536</v>
+        <v>380.4832093744431</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25253,28 +25399,28 @@
         <v>0.163</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3066605656821339</v>
+        <v>0.3040794415414273</v>
       </c>
       <c r="J11" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K11" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1132725440127681</v>
+        <v>0.1129935934771351</v>
       </c>
       <c r="M11" t="n">
-        <v>4.649161751891578</v>
+        <v>4.634172908026552</v>
       </c>
       <c r="N11" t="n">
-        <v>39.26414256238203</v>
+        <v>39.04364284812411</v>
       </c>
       <c r="O11" t="n">
-        <v>6.266110640770878</v>
+        <v>6.248491245742776</v>
       </c>
       <c r="P11" t="n">
-        <v>382.926373953871</v>
+        <v>382.9529301394936</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25331,28 +25477,28 @@
         <v>0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3805693087437491</v>
+        <v>0.3783823201886266</v>
       </c>
       <c r="J12" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K12" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1628274511960328</v>
+        <v>0.163206412232199</v>
       </c>
       <c r="M12" t="n">
-        <v>4.912355683706348</v>
+        <v>4.895220263133017</v>
       </c>
       <c r="N12" t="n">
-        <v>39.71637740806217</v>
+        <v>39.48626674065208</v>
       </c>
       <c r="O12" t="n">
-        <v>6.302093097381391</v>
+        <v>6.283809890556213</v>
       </c>
       <c r="P12" t="n">
-        <v>392.4954979738642</v>
+        <v>392.5179992169705</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25409,28 +25555,28 @@
         <v>0.0619</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5183302365413331</v>
+        <v>0.5197637487762576</v>
       </c>
       <c r="J13" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K13" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1871033333121509</v>
+        <v>0.1909737028378914</v>
       </c>
       <c r="M13" t="n">
-        <v>6.484414286786308</v>
+        <v>6.43799763804101</v>
       </c>
       <c r="N13" t="n">
-        <v>62.25606366388228</v>
+        <v>61.56080910007397</v>
       </c>
       <c r="O13" t="n">
-        <v>7.890251178757383</v>
+        <v>7.846069659394694</v>
       </c>
       <c r="P13" t="n">
-        <v>397.8132498538747</v>
+        <v>397.7986609227234</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25487,28 +25633,28 @@
         <v>0.1021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5696150764418821</v>
+        <v>0.5595447502712503</v>
       </c>
       <c r="J14" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K14" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2502473991954057</v>
+        <v>0.2450238775772615</v>
       </c>
       <c r="M14" t="n">
-        <v>5.721418437288446</v>
+        <v>5.73748188821829</v>
       </c>
       <c r="N14" t="n">
-        <v>51.84729596719342</v>
+        <v>51.89168060485006</v>
       </c>
       <c r="O14" t="n">
-        <v>7.200506646562686</v>
+        <v>7.203588036863994</v>
       </c>
       <c r="P14" t="n">
-        <v>397.2766380768306</v>
+        <v>397.3802459584994</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25565,28 +25711,28 @@
         <v>0.1046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5307162366205763</v>
+        <v>0.5290737738253695</v>
       </c>
       <c r="J15" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K15" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1922863647228709</v>
+        <v>0.1935922823887843</v>
       </c>
       <c r="M15" t="n">
-        <v>5.887992543939589</v>
+        <v>5.859565882479647</v>
       </c>
       <c r="N15" t="n">
-        <v>63.10277036244475</v>
+        <v>62.71947017425047</v>
       </c>
       <c r="O15" t="n">
-        <v>7.943725219470066</v>
+        <v>7.919562498916873</v>
       </c>
       <c r="P15" t="n">
-        <v>394.3794383470629</v>
+        <v>394.3963361214356</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25643,28 +25789,28 @@
         <v>0.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2878999118485573</v>
+        <v>0.2833073994559006</v>
       </c>
       <c r="J16" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K16" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05915645423091231</v>
+        <v>0.05813450142841636</v>
       </c>
       <c r="M16" t="n">
-        <v>6.126556668624543</v>
+        <v>6.113847193575422</v>
       </c>
       <c r="N16" t="n">
-        <v>70.30935121194658</v>
+        <v>69.94779828015774</v>
       </c>
       <c r="O16" t="n">
-        <v>8.385067156078511</v>
+        <v>8.36348003406224</v>
       </c>
       <c r="P16" t="n">
-        <v>385.8389448515294</v>
+        <v>385.8861941632667</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25721,28 +25867,28 @@
         <v>0.0549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3514325375672794</v>
+        <v>0.3549773673879081</v>
       </c>
       <c r="J17" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K17" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08953067727522546</v>
+        <v>0.09235175718621047</v>
       </c>
       <c r="M17" t="n">
-        <v>6.362771713444543</v>
+        <v>6.340859254817548</v>
       </c>
       <c r="N17" t="n">
-        <v>66.98724794924928</v>
+        <v>66.61576410985455</v>
       </c>
       <c r="O17" t="n">
-        <v>8.184573779327136</v>
+        <v>8.161848081767667</v>
       </c>
       <c r="P17" t="n">
-        <v>365.0847213457965</v>
+        <v>365.0482517648035</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -25799,28 +25945,28 @@
         <v>0.1807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4991778336933564</v>
+        <v>-0.4837787224165257</v>
       </c>
       <c r="J18" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K18" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07465785786915091</v>
+        <v>0.07110502368764438</v>
       </c>
       <c r="M18" t="n">
-        <v>7.948966953491484</v>
+        <v>7.919187863411794</v>
       </c>
       <c r="N18" t="n">
-        <v>163.850132095939</v>
+        <v>163.653410853167</v>
       </c>
       <c r="O18" t="n">
-        <v>12.80039577887883</v>
+        <v>12.79270928510326</v>
       </c>
       <c r="P18" t="n">
-        <v>366.1516339851746</v>
+        <v>365.9935861455909</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -25858,7 +26004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S320"/>
+  <dimension ref="A1:S322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56855,7 +57001,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>-36.04772807522905,174.5399249318116</t>
+          <t>-36.047679878203255,174.5399461990183</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -56886,6 +57032,200 @@
       <c r="S320" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-36.04323019136658,174.532089282851</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-36.043760167829774,174.5326944462268</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-36.04429942042188,174.53328138791323</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-36.04475706675952,174.53392328184916</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-36.045147250799275,174.53465625354949</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-36.04562518186259,174.53535525859007</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-36.04603525783037,174.53610163653872</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-36.046432270560494,174.53682420116334</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-36.04684553325406,174.5375350152907</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-36.047146821984335,174.53835803889282</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-36.04742964202437,174.53917594637286</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-36.04763354796034,174.53996664247157</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>-36.04786240592261,174.54071936301148</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-36.047880748455285,174.54149038292275</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-36.047896235655294,174.5422658929856</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>-36.04759703672532,174.54303498644586</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>-36.04729382203473,174.54386837622016</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-36.043224175783386,174.5320973987255</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-36.04375755329078,174.53269796940313</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-36.044296522406015,174.53328503931112</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-36.0447499702411,174.53392994368448</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-36.0451461985621,174.5346571113096</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-36.045619723687324,174.53536035602636</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-36.04603134992675,174.53610539284838</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-36.04643077048563,174.5368254323372</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-36.046836208281064,174.53754131508123</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-36.047147371375885,174.53835765680353</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-36.04743051967134,174.5391753782909</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-36.047645088094406,174.5399615503315</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>-36.04785973479082,174.5407198815407</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-36.0478784155089,174.541490108456</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-36.047893944318034,174.5422645900557</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>-36.04760058513281,174.543038034769</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>-36.047281315596514,174.54385786238805</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0109/nzd0109.xlsx
+++ b/data/nzd0109/nzd0109.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S322"/>
+  <dimension ref="A1:S324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20742,6 +20742,132 @@
       <c r="S322" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="C323" t="n">
+        <v>385.11</v>
+      </c>
+      <c r="D323" t="n">
+        <v>385.32</v>
+      </c>
+      <c r="E323" t="n">
+        <v>389.29</v>
+      </c>
+      <c r="F323" t="n">
+        <v>385.16</v>
+      </c>
+      <c r="G323" t="n">
+        <v>381.12</v>
+      </c>
+      <c r="H323" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="I323" t="n">
+        <v>392.47</v>
+      </c>
+      <c r="J323" t="n">
+        <v>386.17</v>
+      </c>
+      <c r="K323" t="n">
+        <v>389.76</v>
+      </c>
+      <c r="L323" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="M323" t="n">
+        <v>411.24</v>
+      </c>
+      <c r="N323" t="n">
+        <v>406.57</v>
+      </c>
+      <c r="O323" t="n">
+        <v>408.73</v>
+      </c>
+      <c r="P323" t="n">
+        <v>391.12</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="R323" t="n">
+        <v>365.91</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>384.41</v>
+      </c>
+      <c r="C324" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="D324" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="E324" t="n">
+        <v>388.64</v>
+      </c>
+      <c r="F324" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="G324" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="H324" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="I324" t="n">
+        <v>391.67</v>
+      </c>
+      <c r="J324" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="K324" t="n">
+        <v>389.99</v>
+      </c>
+      <c r="L324" t="n">
+        <v>401.29</v>
+      </c>
+      <c r="M324" t="n">
+        <v>411.6</v>
+      </c>
+      <c r="N324" t="n">
+        <v>406.57</v>
+      </c>
+      <c r="O324" t="n">
+        <v>407.55</v>
+      </c>
+      <c r="P324" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>378.09</v>
+      </c>
+      <c r="R324" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20756,7 +20882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24529,6 +24655,26 @@
       </c>
       <c r="B377" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -24697,28 +24843,28 @@
         <v>0.1305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1726698191648065</v>
+        <v>0.1630846666272289</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06303030223842454</v>
+        <v>0.05663341347907314</v>
       </c>
       <c r="M2" t="n">
-        <v>3.82689417061169</v>
+        <v>3.854928424217036</v>
       </c>
       <c r="N2" t="n">
-        <v>23.84033214898674</v>
+        <v>24.03152880411527</v>
       </c>
       <c r="O2" t="n">
-        <v>4.882656259556548</v>
+        <v>4.902196324517743</v>
       </c>
       <c r="P2" t="n">
-        <v>387.3133580910885</v>
+        <v>387.4123761597913</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24775,28 +24921,28 @@
         <v>0.1047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3131999119561787</v>
+        <v>0.2977966268030033</v>
       </c>
       <c r="J3" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K3" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1945462492096458</v>
+        <v>0.1755858767259919</v>
       </c>
       <c r="M3" t="n">
-        <v>3.582648705681317</v>
+        <v>3.653733547694873</v>
       </c>
       <c r="N3" t="n">
-        <v>21.84561552893469</v>
+        <v>22.58617972558081</v>
       </c>
       <c r="O3" t="n">
-        <v>4.673929345736272</v>
+        <v>4.75249194902851</v>
       </c>
       <c r="P3" t="n">
-        <v>389.2136291044506</v>
+        <v>389.3727465701207</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24853,28 +24999,28 @@
         <v>0.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3191723160433066</v>
+        <v>0.301163663903917</v>
       </c>
       <c r="J4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.150598390635289</v>
+        <v>0.1335750089255791</v>
       </c>
       <c r="M4" t="n">
-        <v>4.308506781887044</v>
+        <v>4.380831976930148</v>
       </c>
       <c r="N4" t="n">
-        <v>30.9062601649827</v>
+        <v>31.91231362435276</v>
       </c>
       <c r="O4" t="n">
-        <v>5.559339903710034</v>
+        <v>5.649098478903759</v>
       </c>
       <c r="P4" t="n">
-        <v>391.4094071488811</v>
+        <v>391.5954377814147</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24931,28 +25077,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3471757228578917</v>
+        <v>0.3280155543896578</v>
       </c>
       <c r="J5" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K5" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1535719158202725</v>
+        <v>0.1366705631366653</v>
       </c>
       <c r="M5" t="n">
-        <v>4.232625045298828</v>
+        <v>4.311183924587955</v>
       </c>
       <c r="N5" t="n">
-        <v>35.73388510578212</v>
+        <v>36.86700269074505</v>
       </c>
       <c r="O5" t="n">
-        <v>5.97778262450067</v>
+        <v>6.071820377015862</v>
       </c>
       <c r="P5" t="n">
-        <v>394.7420109234694</v>
+        <v>394.9399466941322</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25009,28 +25155,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3144537235379742</v>
+        <v>0.3048108120352627</v>
       </c>
       <c r="J6" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K6" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1509874496499088</v>
+        <v>0.1435555409976232</v>
       </c>
       <c r="M6" t="n">
-        <v>4.217461112519191</v>
+        <v>4.242819117963453</v>
       </c>
       <c r="N6" t="n">
-        <v>29.90818245886509</v>
+        <v>30.06681104492993</v>
       </c>
       <c r="O6" t="n">
-        <v>5.468837395540764</v>
+        <v>5.483321169230371</v>
       </c>
       <c r="P6" t="n">
-        <v>384.7535347032542</v>
+        <v>384.8531451469661</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25087,28 +25233,28 @@
         <v>0.0857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3919220005002011</v>
+        <v>0.3802017027311899</v>
       </c>
       <c r="J7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1903131083576485</v>
+        <v>0.181160271413076</v>
       </c>
       <c r="M7" t="n">
-        <v>4.551608202607867</v>
+        <v>4.579917689115943</v>
       </c>
       <c r="N7" t="n">
-        <v>35.15207527564811</v>
+        <v>35.44144714601263</v>
       </c>
       <c r="O7" t="n">
-        <v>5.928918558695853</v>
+        <v>5.953271969766931</v>
       </c>
       <c r="P7" t="n">
-        <v>379.6364080812027</v>
+        <v>379.7574866940092</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25165,28 +25311,28 @@
         <v>0.1168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3695210422174468</v>
+        <v>0.3642725251978896</v>
       </c>
       <c r="J8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1594862465730915</v>
+        <v>0.1572674728504624</v>
       </c>
       <c r="M8" t="n">
-        <v>4.72783574134077</v>
+        <v>4.723933506038412</v>
       </c>
       <c r="N8" t="n">
-        <v>38.70822106040094</v>
+        <v>38.57012710692612</v>
       </c>
       <c r="O8" t="n">
-        <v>6.221593128805591</v>
+        <v>6.210485255350512</v>
       </c>
       <c r="P8" t="n">
-        <v>381.1219471468447</v>
+        <v>381.1761664225749</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25243,28 +25389,28 @@
         <v>0.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4133675917702815</v>
+        <v>0.4091664680705172</v>
       </c>
       <c r="J9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2205175680832676</v>
+        <v>0.2191672403326215</v>
       </c>
       <c r="M9" t="n">
-        <v>4.453976355897998</v>
+        <v>4.448260798440105</v>
       </c>
       <c r="N9" t="n">
-        <v>32.48921842451829</v>
+        <v>32.35413891213755</v>
       </c>
       <c r="O9" t="n">
-        <v>5.6999314403349</v>
+        <v>5.688069875813548</v>
       </c>
       <c r="P9" t="n">
-        <v>384.4311974395648</v>
+        <v>384.474601570359</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25321,28 +25467,28 @@
         <v>0.101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3703324768849427</v>
+        <v>0.3651138774650018</v>
       </c>
       <c r="J10" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K10" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1371782508535999</v>
+        <v>0.1353004520458428</v>
       </c>
       <c r="M10" t="n">
-        <v>5.184723624607617</v>
+        <v>5.176861496026669</v>
       </c>
       <c r="N10" t="n">
-        <v>46.40050422409453</v>
+        <v>46.21362685443464</v>
       </c>
       <c r="O10" t="n">
-        <v>6.811791557592946</v>
+        <v>6.798060521533671</v>
       </c>
       <c r="P10" t="n">
-        <v>380.4832093744431</v>
+        <v>380.5371193673245</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25399,28 +25545,28 @@
         <v>0.163</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3040794415414273</v>
+        <v>0.302662606281062</v>
       </c>
       <c r="J11" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K11" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1129935934771351</v>
+        <v>0.1135026201095573</v>
       </c>
       <c r="M11" t="n">
-        <v>4.634172908026552</v>
+        <v>4.613115989063106</v>
       </c>
       <c r="N11" t="n">
-        <v>39.04364284812411</v>
+        <v>38.8093610930623</v>
       </c>
       <c r="O11" t="n">
-        <v>6.248491245742776</v>
+        <v>6.229715972101962</v>
       </c>
       <c r="P11" t="n">
-        <v>382.9529301394936</v>
+        <v>382.9675653072218</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25477,28 +25623,28 @@
         <v>0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3783823201886266</v>
+        <v>0.3770888766301763</v>
       </c>
       <c r="J12" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K12" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L12" t="n">
-        <v>0.163206412232199</v>
+        <v>0.1642455163767516</v>
       </c>
       <c r="M12" t="n">
-        <v>4.895220263133017</v>
+        <v>4.872766606155658</v>
       </c>
       <c r="N12" t="n">
-        <v>39.48626674065208</v>
+        <v>39.24822535309261</v>
       </c>
       <c r="O12" t="n">
-        <v>6.283809890556213</v>
+        <v>6.264840409227725</v>
       </c>
       <c r="P12" t="n">
-        <v>392.5179992169705</v>
+        <v>392.5313635940277</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25555,28 +25701,28 @@
         <v>0.0619</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5197637487762576</v>
+        <v>0.51963702054557</v>
       </c>
       <c r="J13" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K13" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1909737028378914</v>
+        <v>0.1931633225846386</v>
       </c>
       <c r="M13" t="n">
-        <v>6.43799763804101</v>
+        <v>6.399096477838861</v>
       </c>
       <c r="N13" t="n">
-        <v>61.56080910007397</v>
+        <v>61.17986605930534</v>
       </c>
       <c r="O13" t="n">
-        <v>7.846069659394694</v>
+        <v>7.82175594475469</v>
       </c>
       <c r="P13" t="n">
-        <v>397.7986609227234</v>
+        <v>397.7999680215012</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25633,28 +25779,28 @@
         <v>0.1021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5595447502712503</v>
+        <v>0.5523977424430734</v>
       </c>
       <c r="J14" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K14" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2450238775772615</v>
+        <v>0.2423048089594488</v>
       </c>
       <c r="M14" t="n">
-        <v>5.73748188821829</v>
+        <v>5.738157292255106</v>
       </c>
       <c r="N14" t="n">
-        <v>51.89168060485006</v>
+        <v>51.75873768493716</v>
       </c>
       <c r="O14" t="n">
-        <v>7.203588036863994</v>
+        <v>7.194354570420974</v>
       </c>
       <c r="P14" t="n">
-        <v>397.3802459584994</v>
+        <v>397.4540773861347</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25711,28 +25857,28 @@
         <v>0.1046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5290737738253695</v>
+        <v>0.5287930243786367</v>
       </c>
       <c r="J15" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K15" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1935922823887843</v>
+        <v>0.1957085360317158</v>
       </c>
       <c r="M15" t="n">
-        <v>5.859565882479647</v>
+        <v>5.827072715095318</v>
       </c>
       <c r="N15" t="n">
-        <v>62.71947017425047</v>
+        <v>62.33364379095666</v>
       </c>
       <c r="O15" t="n">
-        <v>7.919562498916873</v>
+        <v>7.895165849490222</v>
       </c>
       <c r="P15" t="n">
-        <v>394.3963361214356</v>
+        <v>394.3992436331226</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25789,28 +25935,28 @@
         <v>0.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2833073994559006</v>
+        <v>0.2808387798811703</v>
       </c>
       <c r="J16" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K16" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05813450142841636</v>
+        <v>0.05795770639693565</v>
       </c>
       <c r="M16" t="n">
-        <v>6.113847193575422</v>
+        <v>6.089652452459847</v>
       </c>
       <c r="N16" t="n">
-        <v>69.94779828015774</v>
+        <v>69.53776923554136</v>
       </c>
       <c r="O16" t="n">
-        <v>8.36348003406224</v>
+        <v>8.338930940806582</v>
       </c>
       <c r="P16" t="n">
-        <v>385.8861941632667</v>
+        <v>385.9116921850358</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25867,28 +26013,28 @@
         <v>0.0549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3549773673879081</v>
+        <v>0.359612861378737</v>
       </c>
       <c r="J17" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K17" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09235175718621047</v>
+        <v>0.09570384542070109</v>
       </c>
       <c r="M17" t="n">
-        <v>6.340859254817548</v>
+        <v>6.324449924167721</v>
       </c>
       <c r="N17" t="n">
-        <v>66.61576410985455</v>
+        <v>66.28253591247797</v>
       </c>
       <c r="O17" t="n">
-        <v>8.161848081767667</v>
+        <v>8.141408717935612</v>
       </c>
       <c r="P17" t="n">
-        <v>365.0482517648035</v>
+        <v>365.0003647458365</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -25945,28 +26091,28 @@
         <v>0.1807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4837787224165257</v>
+        <v>-0.4673535771373748</v>
       </c>
       <c r="J18" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K18" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07110502368764438</v>
+        <v>0.06724582354562225</v>
       </c>
       <c r="M18" t="n">
-        <v>7.919187863411794</v>
+        <v>7.891903419764105</v>
       </c>
       <c r="N18" t="n">
-        <v>163.653410853167</v>
+        <v>163.5925886621643</v>
       </c>
       <c r="O18" t="n">
-        <v>12.79270928510326</v>
+        <v>12.79033184331682</v>
       </c>
       <c r="P18" t="n">
-        <v>365.9935861455909</v>
+        <v>365.8243409089604</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26004,7 +26150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S322"/>
+  <dimension ref="A1:S324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57229,6 +57375,200 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-36.043216944930165,174.532107154169</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-36.0437498920829,174.5327082931277</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-36.04428259932837,174.5333025818929</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-36.04473857280169,174.5339406429933</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-36.045138081303755,174.5346637283153</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-36.04560859188188,174.53537075211133</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-36.046024670963945,174.53611181272217</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-36.04642071998369,174.5368336812009</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-36.04682309009821,174.53755017749597</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-36.04714117109976,174.53836196895378</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-36.04742301977897,174.53918023280917</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-36.0476265050843,174.53996975017398</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>-36.04784263954729,174.54072320012702</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-36.04786468701665,174.541488493325</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-36.0478848608023,174.54225942487022</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>-36.047592083739694,174.54303073149518</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>-36.04727804010063,174.54385510876588</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-36.04321676263974,174.53210740010454</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-36.043745514249466,174.532714192398</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-36.044276740294954,174.53330996406348</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-36.04474323213238,174.5339362690624</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-36.04513244431857,174.5346683234574</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-36.04561261369556,174.53536699610677</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-36.046024670963945,174.53611181272217</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-36.04642672028341,174.53682875650642</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-36.046822853022604,174.53755033766006</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-36.047139365956056,174.53836322438983</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-36.04742629100865,174.53917811541302</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-36.04762345034286,174.53997109809293</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>-36.04784263954729,174.54072320012702</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-36.047875275004145,174.5414897389815</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-36.04787970529325,174.54225649327898</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>-36.04759119663778,174.54302996941453</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>-36.047280198950205,174.54385692365318</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0109/nzd0109.xlsx
+++ b/data/nzd0109/nzd0109.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S324"/>
+  <dimension ref="A1:S328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20866,6 +20866,258 @@
         <v>365.62</v>
       </c>
       <c r="S324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>389.21</v>
+      </c>
+      <c r="C325" t="n">
+        <v>391.45</v>
+      </c>
+      <c r="D325" t="n">
+        <v>395.15</v>
+      </c>
+      <c r="E325" t="n">
+        <v>395.84</v>
+      </c>
+      <c r="F325" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="G325" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="H325" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="I325" t="n">
+        <v>395.66</v>
+      </c>
+      <c r="J325" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="K325" t="n">
+        <v>393.71</v>
+      </c>
+      <c r="L325" t="n">
+        <v>405.08</v>
+      </c>
+      <c r="M325" t="n">
+        <v>422.28</v>
+      </c>
+      <c r="N325" t="n">
+        <v>413.09</v>
+      </c>
+      <c r="O325" t="n">
+        <v>410.94</v>
+      </c>
+      <c r="P325" t="n">
+        <v>396.17</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>386.21</v>
+      </c>
+      <c r="R325" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>387.76</v>
+      </c>
+      <c r="C326" t="n">
+        <v>391.34</v>
+      </c>
+      <c r="D326" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="E326" t="n">
+        <v>394.95</v>
+      </c>
+      <c r="F326" t="n">
+        <v>391.44</v>
+      </c>
+      <c r="G326" t="n">
+        <v>387.25</v>
+      </c>
+      <c r="H326" t="n">
+        <v>389.77</v>
+      </c>
+      <c r="I326" t="n">
+        <v>394.54</v>
+      </c>
+      <c r="J326" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="K326" t="n">
+        <v>392.38</v>
+      </c>
+      <c r="L326" t="n">
+        <v>404.66</v>
+      </c>
+      <c r="M326" t="n">
+        <v>419.29</v>
+      </c>
+      <c r="N326" t="n">
+        <v>411.63</v>
+      </c>
+      <c r="O326" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="P326" t="n">
+        <v>396.09</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>385.57</v>
+      </c>
+      <c r="R326" t="n">
+        <v>365.69</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="C327" t="n">
+        <v>391.91</v>
+      </c>
+      <c r="D327" t="n">
+        <v>393.45</v>
+      </c>
+      <c r="E327" t="n">
+        <v>394.76</v>
+      </c>
+      <c r="F327" t="n">
+        <v>389.91</v>
+      </c>
+      <c r="G327" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="H327" t="n">
+        <v>388.36</v>
+      </c>
+      <c r="I327" t="n">
+        <v>393.91</v>
+      </c>
+      <c r="J327" t="n">
+        <v>387.93</v>
+      </c>
+      <c r="K327" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="L327" t="n">
+        <v>404.31</v>
+      </c>
+      <c r="M327" t="n">
+        <v>413.09</v>
+      </c>
+      <c r="N327" t="n">
+        <v>408.33</v>
+      </c>
+      <c r="O327" t="n">
+        <v>408.44</v>
+      </c>
+      <c r="P327" t="n">
+        <v>395.98</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>384.84</v>
+      </c>
+      <c r="R327" t="n">
+        <v>365</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="C328" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="D328" t="n">
+        <v>392.92</v>
+      </c>
+      <c r="E328" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="F328" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="G328" t="n">
+        <v>385.65</v>
+      </c>
+      <c r="H328" t="n">
+        <v>388.32</v>
+      </c>
+      <c r="I328" t="n">
+        <v>393.61</v>
+      </c>
+      <c r="J328" t="n">
+        <v>387.67</v>
+      </c>
+      <c r="K328" t="n">
+        <v>391.08</v>
+      </c>
+      <c r="L328" t="n">
+        <v>404.26</v>
+      </c>
+      <c r="M328" t="n">
+        <v>411.89</v>
+      </c>
+      <c r="N328" t="n">
+        <v>408.73</v>
+      </c>
+      <c r="O328" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="P328" t="n">
+        <v>395.46</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>383.62</v>
+      </c>
+      <c r="R328" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="S328" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20882,7 +21134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B379"/>
+  <dimension ref="A1:B383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24675,6 +24927,46 @@
       </c>
       <c r="B379" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>
@@ -24843,28 +25135,28 @@
         <v>0.1305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1630846666272289</v>
+        <v>0.1517625879923664</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05663341347907314</v>
+        <v>0.05030726733794477</v>
       </c>
       <c r="M2" t="n">
-        <v>3.854928424217036</v>
+        <v>3.868496880557298</v>
       </c>
       <c r="N2" t="n">
-        <v>24.03152880411527</v>
+        <v>23.99451136913061</v>
       </c>
       <c r="O2" t="n">
-        <v>4.902196324517743</v>
+        <v>4.898419272492975</v>
       </c>
       <c r="P2" t="n">
-        <v>387.4123761597913</v>
+        <v>387.5307733837099</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24921,28 +25213,28 @@
         <v>0.1047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2977966268030033</v>
+        <v>0.2837039495174909</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1755858767259919</v>
+        <v>0.163789768662655</v>
       </c>
       <c r="M3" t="n">
-        <v>3.653733547694873</v>
+        <v>3.694327094628969</v>
       </c>
       <c r="N3" t="n">
-        <v>22.58617972558081</v>
+        <v>22.67720604674129</v>
       </c>
       <c r="O3" t="n">
-        <v>4.75249194902851</v>
+        <v>4.762059013361898</v>
       </c>
       <c r="P3" t="n">
-        <v>389.3727465701207</v>
+        <v>389.5200657022508</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24999,28 +25291,28 @@
         <v>0.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.301163663903917</v>
+        <v>0.2864987695865829</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1335750089255791</v>
+        <v>0.1242534098469399</v>
       </c>
       <c r="M4" t="n">
-        <v>4.380831976930148</v>
+        <v>4.407275936194547</v>
       </c>
       <c r="N4" t="n">
-        <v>31.91231362435276</v>
+        <v>31.92609022456119</v>
       </c>
       <c r="O4" t="n">
-        <v>5.649098478903759</v>
+        <v>5.650317710055001</v>
       </c>
       <c r="P4" t="n">
-        <v>391.5954377814147</v>
+        <v>391.7487685001003</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25077,28 +25369,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3280155543896578</v>
+        <v>0.3062229555471437</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1366705631366653</v>
+        <v>0.1218560187776294</v>
       </c>
       <c r="M5" t="n">
-        <v>4.311183924587955</v>
+        <v>4.378392590827981</v>
       </c>
       <c r="N5" t="n">
-        <v>36.86700269074505</v>
+        <v>37.29274115638454</v>
       </c>
       <c r="O5" t="n">
-        <v>6.071820377015862</v>
+        <v>6.10677829599082</v>
       </c>
       <c r="P5" t="n">
-        <v>394.9399466941322</v>
+        <v>395.1677817890126</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25155,28 +25447,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3048108120352627</v>
+        <v>0.2992799104029717</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1435555409976232</v>
+        <v>0.1423560743070131</v>
       </c>
       <c r="M6" t="n">
-        <v>4.242819117963453</v>
+        <v>4.219270525705732</v>
       </c>
       <c r="N6" t="n">
-        <v>30.06681104492993</v>
+        <v>29.7794188616616</v>
       </c>
       <c r="O6" t="n">
-        <v>5.483321169230371</v>
+        <v>5.457052213572966</v>
       </c>
       <c r="P6" t="n">
-        <v>384.8531451469661</v>
+        <v>384.9110031010254</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25233,28 +25525,28 @@
         <v>0.0857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3802017027311899</v>
+        <v>0.3722076343538036</v>
       </c>
       <c r="J7" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.181160271413076</v>
+        <v>0.1787181271907691</v>
       </c>
       <c r="M7" t="n">
-        <v>4.579917689115943</v>
+        <v>4.560819414018943</v>
       </c>
       <c r="N7" t="n">
-        <v>35.44144714601263</v>
+        <v>35.13373012423538</v>
       </c>
       <c r="O7" t="n">
-        <v>5.953271969766931</v>
+        <v>5.927371265935295</v>
       </c>
       <c r="P7" t="n">
-        <v>379.7574866940092</v>
+        <v>379.841079875228</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25311,28 +25603,28 @@
         <v>0.1168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3642725251978896</v>
+        <v>0.3602444344005942</v>
       </c>
       <c r="J8" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1572674728504624</v>
+        <v>0.1580874255836706</v>
       </c>
       <c r="M8" t="n">
-        <v>4.723933506038412</v>
+        <v>4.684865593377005</v>
       </c>
       <c r="N8" t="n">
-        <v>38.57012710692612</v>
+        <v>38.14119569988275</v>
       </c>
       <c r="O8" t="n">
-        <v>6.210485255350512</v>
+        <v>6.175855867803486</v>
       </c>
       <c r="P8" t="n">
-        <v>381.1761664225749</v>
+        <v>381.2183028688892</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25389,28 +25681,28 @@
         <v>0.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4091664680705172</v>
+        <v>0.4067275319292188</v>
       </c>
       <c r="J9" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K9" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2191672403326215</v>
+        <v>0.2220900039824218</v>
       </c>
       <c r="M9" t="n">
-        <v>4.448260798440105</v>
+        <v>4.407983674130029</v>
       </c>
       <c r="N9" t="n">
-        <v>32.35413891213755</v>
+        <v>31.97698830443313</v>
       </c>
       <c r="O9" t="n">
-        <v>5.688069875813548</v>
+        <v>5.654819917949035</v>
       </c>
       <c r="P9" t="n">
-        <v>384.474601570359</v>
+        <v>384.500118870418</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25467,28 +25759,28 @@
         <v>0.101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3651138774650018</v>
+        <v>0.3619072609494087</v>
       </c>
       <c r="J10" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K10" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1353004520458428</v>
+        <v>0.1365897774528119</v>
       </c>
       <c r="M10" t="n">
-        <v>5.176861496026669</v>
+        <v>5.13324366191047</v>
       </c>
       <c r="N10" t="n">
-        <v>46.21362685443464</v>
+        <v>45.69026288635207</v>
       </c>
       <c r="O10" t="n">
-        <v>6.798060521533671</v>
+        <v>6.759457292294409</v>
       </c>
       <c r="P10" t="n">
-        <v>380.5371193673245</v>
+        <v>380.5706766940994</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25545,28 +25837,28 @@
         <v>0.163</v>
       </c>
       <c r="I11" t="n">
-        <v>0.302662606281062</v>
+        <v>0.3054870607278242</v>
       </c>
       <c r="J11" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K11" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1135026201095573</v>
+        <v>0.1183603829679729</v>
       </c>
       <c r="M11" t="n">
-        <v>4.613115989063106</v>
+        <v>4.568404456994724</v>
       </c>
       <c r="N11" t="n">
-        <v>38.8093610930623</v>
+        <v>38.36193016866397</v>
       </c>
       <c r="O11" t="n">
-        <v>6.229715972101962</v>
+        <v>6.193700845913045</v>
       </c>
       <c r="P11" t="n">
-        <v>382.9675653072218</v>
+        <v>382.9380638282551</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25623,28 +25915,28 @@
         <v>0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3770888766301763</v>
+        <v>0.3820908006187336</v>
       </c>
       <c r="J12" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K12" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1642455163767516</v>
+        <v>0.171888138940269</v>
       </c>
       <c r="M12" t="n">
-        <v>4.872766606155658</v>
+        <v>4.830288962421688</v>
       </c>
       <c r="N12" t="n">
-        <v>39.24822535309261</v>
+        <v>38.81560269139588</v>
       </c>
       <c r="O12" t="n">
-        <v>6.264840409227725</v>
+        <v>6.230216905645893</v>
       </c>
       <c r="P12" t="n">
-        <v>392.5313635940277</v>
+        <v>392.4790809547619</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25701,28 +25993,28 @@
         <v>0.0619</v>
       </c>
       <c r="I13" t="n">
-        <v>0.51963702054557</v>
+        <v>0.5321620911320453</v>
       </c>
       <c r="J13" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K13" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1931633225846386</v>
+        <v>0.2040886589186378</v>
       </c>
       <c r="M13" t="n">
-        <v>6.399096477838861</v>
+        <v>6.388617149517646</v>
       </c>
       <c r="N13" t="n">
-        <v>61.17986605930534</v>
+        <v>60.94860424193227</v>
       </c>
       <c r="O13" t="n">
-        <v>7.82175594475469</v>
+        <v>7.806958706303772</v>
       </c>
       <c r="P13" t="n">
-        <v>397.7999680215012</v>
+        <v>397.6691384887971</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25779,28 +26071,28 @@
         <v>0.1021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5523977424430734</v>
+        <v>0.5479615900985114</v>
       </c>
       <c r="J14" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K14" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2423048089594488</v>
+        <v>0.2444680130502717</v>
       </c>
       <c r="M14" t="n">
-        <v>5.738157292255106</v>
+        <v>5.695610310822764</v>
       </c>
       <c r="N14" t="n">
-        <v>51.75873768493716</v>
+        <v>51.21074839193048</v>
       </c>
       <c r="O14" t="n">
-        <v>7.194354570420974</v>
+        <v>7.15616855530461</v>
       </c>
       <c r="P14" t="n">
-        <v>397.4540773861347</v>
+        <v>397.5005024129938</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25857,28 +26149,28 @@
         <v>0.1046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5287930243786367</v>
+        <v>0.5303284319303232</v>
       </c>
       <c r="J15" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K15" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1957085360317158</v>
+        <v>0.2012503310002559</v>
       </c>
       <c r="M15" t="n">
-        <v>5.827072715095318</v>
+        <v>5.771960000594944</v>
       </c>
       <c r="N15" t="n">
-        <v>62.33364379095666</v>
+        <v>61.60188266178473</v>
       </c>
       <c r="O15" t="n">
-        <v>7.895165849490222</v>
+        <v>7.848686683884427</v>
       </c>
       <c r="P15" t="n">
-        <v>394.3992436331226</v>
+        <v>394.3832306126959</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25935,28 +26227,28 @@
         <v>0.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2808387798811703</v>
+        <v>0.2871901427106678</v>
       </c>
       <c r="J16" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K16" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05795770639693565</v>
+        <v>0.0620842978167685</v>
       </c>
       <c r="M16" t="n">
-        <v>6.089652452459847</v>
+        <v>6.040538807653324</v>
       </c>
       <c r="N16" t="n">
-        <v>69.53776923554136</v>
+        <v>68.76242228570156</v>
       </c>
       <c r="O16" t="n">
-        <v>8.338930940806582</v>
+        <v>8.292311034066532</v>
       </c>
       <c r="P16" t="n">
-        <v>385.9116921850358</v>
+        <v>385.8453004358649</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26013,28 +26305,28 @@
         <v>0.0549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.359612861378737</v>
+        <v>0.3860186333401942</v>
       </c>
       <c r="J17" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K17" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09570384542070109</v>
+        <v>0.1096575912771246</v>
       </c>
       <c r="M17" t="n">
-        <v>6.324449924167721</v>
+        <v>6.374747805966182</v>
       </c>
       <c r="N17" t="n">
-        <v>66.28253591247797</v>
+        <v>66.76747782972232</v>
       </c>
       <c r="O17" t="n">
-        <v>8.141408717935612</v>
+        <v>8.17113687498394</v>
       </c>
       <c r="P17" t="n">
-        <v>365.0003647458365</v>
+        <v>364.7243386693597</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26091,28 +26383,28 @@
         <v>0.1807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4673535771373748</v>
+        <v>-0.4357477480276673</v>
       </c>
       <c r="J18" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K18" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06724582354562225</v>
+        <v>0.06005766137647028</v>
       </c>
       <c r="M18" t="n">
-        <v>7.891903419764105</v>
+        <v>7.84278820543279</v>
       </c>
       <c r="N18" t="n">
-        <v>163.5925886621643</v>
+        <v>163.3685619356522</v>
       </c>
       <c r="O18" t="n">
-        <v>12.79033184331682</v>
+        <v>12.7815711841562</v>
       </c>
       <c r="P18" t="n">
-        <v>365.8243409089604</v>
+        <v>365.4948580536197</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26150,7 +26442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S324"/>
+  <dimension ref="A1:S328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57569,6 +57861,394 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-36.043187596165204,174.5321467497743</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-36.04371134281775,174.53276023945753</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-36.04422066995326,174.53338061058673</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-36.04469162107639,174.53398471872998</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-36.045081110165995,174.53471016985478</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-36.04556097647221,174.53541522049363</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-36.04599632089482,174.53613906302562</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-36.046396793786634,174.53685331841282</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-36.04678405164678,174.537576551171</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-36.047110169716966,174.53838352969524</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-36.047396052079314,174.53919768840996</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-36.04753282634046,174.54001108630953</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-36.04778458694874,174.54073446948325</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-36.04784485697218,174.5414861603592</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-36.04784353489403,174.54223592561823</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>-36.04753116939533,174.5429784019971</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>-36.047267394738505,174.54384615949553</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-36.043196406872354,174.53213486289798</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-36.04371201165377,174.53275933818094</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-36.04422930100846,174.53336973579138</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-36.044698000777366,174.5339787298161</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-36.0450908809428,174.53470220495163</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-36.04556456737846,174.53541186692217</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-36.04600342617586,174.5361322333775</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-36.04640519420726,174.53684642384442</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-36.04679796008353,174.53756715488484</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-36.04712060815764,174.5383762700044</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-36.04739940309538,174.53919551937145</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-36.047558197668224,174.53999989111549</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-36.0477975864571,174.54073194597842</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-36.047853381199445,174.54148716321762</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-36.04784418956192,174.54223629788342</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>-36.047535900607464,174.54298246642122</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>-36.047279677848586,174.54385648557695</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-36.043205278341865,174.5321228940405</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-36.04370854586707,174.53276400843217</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-36.044231380021614,174.53336711631476</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-36.044699362735976,174.53397745128382</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-36.045102380394866,174.53469283087085</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-36.04557139010009,174.53540549513554</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-36.04601344462148,174.5361226035715</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-36.04640991944368,174.5368425456491</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-36.04680918166268,174.537559573788</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-36.04712759327938,174.53837141201473</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-36.04740219560873,174.53919371183923</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-36.04761080710731,174.53997667697863</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-36.0478269689073,174.54072624216332</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-36.047867289149174,174.5414887994609</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-36.047845089730295,174.54223680974803</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-36.047541297146104,174.54298710240556</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>-36.04728481442161,174.5438608037574</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-36.04320789117172,174.5321193689655</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-36.04370641775235,174.53276687613007</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-36.04423471904262,174.5333629092763</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-36.04469979282816,174.53397704753678</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-36.04510839317999,174.53468792938963</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-36.04557605827787,174.5354011354914</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-36.0460137288327,174.53612233038544</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-36.04641216955624,174.53684069888928</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-36.04681123631798,174.5375581856996</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-36.0471308111444,174.53836917406417</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-36.04740259453923,174.53919345362033</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-36.04762098957892,174.53997218391646</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-36.047823407398205,174.54072693353504</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-36.04787904360985,174.54149018235088</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-36.04784934507156,174.54223922947193</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>-36.04755031601845,174.54299485021647</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>-36.0472887599051,174.54386412062107</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0109/nzd0109.xlsx
+++ b/data/nzd0109/nzd0109.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S328"/>
+  <dimension ref="A1:S330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21120,6 +21120,132 @@
       <c r="S328" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="C329" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="D329" t="n">
+        <v>391.87</v>
+      </c>
+      <c r="E329" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="F329" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="G329" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="H329" t="n">
+        <v>384.48</v>
+      </c>
+      <c r="I329" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="J329" t="n">
+        <v>384.75</v>
+      </c>
+      <c r="K329" t="n">
+        <v>388.27</v>
+      </c>
+      <c r="L329" t="n">
+        <v>401.19</v>
+      </c>
+      <c r="M329" t="n">
+        <v>408.43</v>
+      </c>
+      <c r="N329" t="n">
+        <v>408.73</v>
+      </c>
+      <c r="O329" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="P329" t="n">
+        <v>395.46</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>383.62</v>
+      </c>
+      <c r="R329" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="C330" t="n">
+        <v>392.03</v>
+      </c>
+      <c r="D330" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="E330" t="n">
+        <v>395.76</v>
+      </c>
+      <c r="F330" t="n">
+        <v>389.31</v>
+      </c>
+      <c r="G330" t="n">
+        <v>383.81</v>
+      </c>
+      <c r="H330" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="I330" t="n">
+        <v>390.97</v>
+      </c>
+      <c r="J330" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="K330" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="L330" t="n">
+        <v>400.9</v>
+      </c>
+      <c r="M330" t="n">
+        <v>406.46</v>
+      </c>
+      <c r="N330" t="n">
+        <v>411.08</v>
+      </c>
+      <c r="O330" t="n">
+        <v>406.31</v>
+      </c>
+      <c r="P330" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="R330" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21134,7 +21260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B383"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24967,6 +25093,26 @@
       </c>
       <c r="B383" t="n">
         <v>-0.15</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -25135,28 +25281,28 @@
         <v>0.1305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1517625879923664</v>
+        <v>0.1431654983948006</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05030726733794477</v>
+        <v>0.04512400597998267</v>
       </c>
       <c r="M2" t="n">
-        <v>3.868496880557298</v>
+        <v>3.892474564318504</v>
       </c>
       <c r="N2" t="n">
-        <v>23.99451136913061</v>
+        <v>24.13534083426074</v>
       </c>
       <c r="O2" t="n">
-        <v>4.898419272492975</v>
+        <v>4.912773232529744</v>
       </c>
       <c r="P2" t="n">
-        <v>387.5307733837099</v>
+        <v>387.6209629650679</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25213,28 +25359,28 @@
         <v>0.1047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2837039495174909</v>
+        <v>0.2764029024581089</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L3" t="n">
-        <v>0.163789768662655</v>
+        <v>0.1574632398679348</v>
       </c>
       <c r="M3" t="n">
-        <v>3.694327094628969</v>
+        <v>3.715837444757653</v>
       </c>
       <c r="N3" t="n">
-        <v>22.67720604674129</v>
+        <v>22.74742511143613</v>
       </c>
       <c r="O3" t="n">
-        <v>4.762059013361898</v>
+        <v>4.769426077782957</v>
       </c>
       <c r="P3" t="n">
-        <v>389.5200657022508</v>
+        <v>389.5966579726113</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25291,28 +25437,28 @@
         <v>0.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2864987695865829</v>
+        <v>0.2769208946872855</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1242534098469399</v>
+        <v>0.1173896329759349</v>
       </c>
       <c r="M4" t="n">
-        <v>4.407275936194547</v>
+        <v>4.432703944503235</v>
       </c>
       <c r="N4" t="n">
-        <v>31.92609022456119</v>
+        <v>32.08397002208002</v>
       </c>
       <c r="O4" t="n">
-        <v>5.650317710055001</v>
+        <v>5.664271358443204</v>
       </c>
       <c r="P4" t="n">
-        <v>391.7487685001003</v>
+        <v>391.849252681375</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25369,28 +25515,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3062229555471437</v>
+        <v>0.2960838325480497</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1218560187776294</v>
+        <v>0.1152158901001203</v>
       </c>
       <c r="M5" t="n">
-        <v>4.378392590827981</v>
+        <v>4.408894389800403</v>
       </c>
       <c r="N5" t="n">
-        <v>37.29274115638454</v>
+        <v>37.46206324012164</v>
       </c>
       <c r="O5" t="n">
-        <v>6.10677829599082</v>
+        <v>6.120626049688189</v>
       </c>
       <c r="P5" t="n">
-        <v>395.1677817890126</v>
+        <v>395.2741502900037</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25447,28 +25593,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2992799104029717</v>
+        <v>0.2946505559386747</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1423560743070131</v>
+        <v>0.1399858379639491</v>
       </c>
       <c r="M6" t="n">
-        <v>4.219270525705732</v>
+        <v>4.217187030401299</v>
       </c>
       <c r="N6" t="n">
-        <v>29.7794188616616</v>
+        <v>29.68064957572417</v>
       </c>
       <c r="O6" t="n">
-        <v>5.457052213572966</v>
+        <v>5.447995005111896</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9110031010254</v>
+        <v>384.959570020494</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25525,28 +25671,28 @@
         <v>0.0857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3722076343538036</v>
+        <v>0.3641907590333776</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1787181271907691</v>
+        <v>0.1734647041783922</v>
       </c>
       <c r="M7" t="n">
-        <v>4.560819414018943</v>
+        <v>4.569594737490191</v>
       </c>
       <c r="N7" t="n">
-        <v>35.13373012423538</v>
+        <v>35.16782407015932</v>
       </c>
       <c r="O7" t="n">
-        <v>5.927371265935295</v>
+        <v>5.930246543792199</v>
       </c>
       <c r="P7" t="n">
-        <v>379.841079875228</v>
+        <v>379.925184000182</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25603,28 +25749,28 @@
         <v>0.1168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3602444344005942</v>
+        <v>0.3519537646276184</v>
       </c>
       <c r="J8" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1580874255836706</v>
+        <v>0.1529521519695144</v>
       </c>
       <c r="M8" t="n">
-        <v>4.684865593377005</v>
+        <v>4.695452934316635</v>
       </c>
       <c r="N8" t="n">
-        <v>38.14119569988275</v>
+        <v>38.17340955775279</v>
       </c>
       <c r="O8" t="n">
-        <v>6.175855867803486</v>
+        <v>6.178463365413183</v>
       </c>
       <c r="P8" t="n">
-        <v>381.2183028688892</v>
+        <v>381.3052835363261</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25681,28 +25827,28 @@
         <v>0.1006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4067275319292188</v>
+        <v>0.4010798942359858</v>
       </c>
       <c r="J9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2220900039824218</v>
+        <v>0.2190973432060023</v>
       </c>
       <c r="M9" t="n">
-        <v>4.407983674130029</v>
+        <v>4.409741084179814</v>
       </c>
       <c r="N9" t="n">
-        <v>31.97698830443313</v>
+        <v>31.9050142394094</v>
       </c>
       <c r="O9" t="n">
-        <v>5.654819917949035</v>
+        <v>5.648452375598948</v>
       </c>
       <c r="P9" t="n">
-        <v>384.500118870418</v>
+        <v>384.5593687373185</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25759,28 +25905,28 @@
         <v>0.101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3619072609494087</v>
+        <v>0.3550332611358004</v>
       </c>
       <c r="J10" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K10" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1365897774528119</v>
+        <v>0.1333289426483788</v>
       </c>
       <c r="M10" t="n">
-        <v>5.13324366191047</v>
+        <v>5.13296040599086</v>
       </c>
       <c r="N10" t="n">
-        <v>45.69026288635207</v>
+        <v>45.593749830712</v>
       </c>
       <c r="O10" t="n">
-        <v>6.759457292294409</v>
+        <v>6.752314405499199</v>
       </c>
       <c r="P10" t="n">
-        <v>380.5706766940994</v>
+        <v>380.6427932760456</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25837,28 +25983,28 @@
         <v>0.163</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3054870607278242</v>
+        <v>0.3021130138137141</v>
       </c>
       <c r="J11" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K11" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1183603829679729</v>
+        <v>0.1174289599511333</v>
       </c>
       <c r="M11" t="n">
-        <v>4.568404456994724</v>
+        <v>4.559144494035927</v>
       </c>
       <c r="N11" t="n">
-        <v>38.36193016866397</v>
+        <v>38.17250803763586</v>
       </c>
       <c r="O11" t="n">
-        <v>6.193700845913045</v>
+        <v>6.178390408321237</v>
       </c>
       <c r="P11" t="n">
-        <v>382.9380638282551</v>
+        <v>382.9734608357995</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25915,28 +26061,28 @@
         <v>0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3820908006187336</v>
+        <v>0.3800172540645162</v>
       </c>
       <c r="J12" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K12" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L12" t="n">
-        <v>0.171888138940269</v>
+        <v>0.1723283789804525</v>
       </c>
       <c r="M12" t="n">
-        <v>4.830288962421688</v>
+        <v>4.813761455686603</v>
       </c>
       <c r="N12" t="n">
-        <v>38.81560269139588</v>
+        <v>38.59626351455375</v>
       </c>
       <c r="O12" t="n">
-        <v>6.230216905645893</v>
+        <v>6.212589115220299</v>
       </c>
       <c r="P12" t="n">
-        <v>392.4790809547619</v>
+        <v>392.5008358091598</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25993,28 +26139,28 @@
         <v>0.0619</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5321620911320453</v>
+        <v>0.5265845713317698</v>
       </c>
       <c r="J13" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K13" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2040886589186378</v>
+        <v>0.2026737092527565</v>
       </c>
       <c r="M13" t="n">
-        <v>6.388617149517646</v>
+        <v>6.373145412808097</v>
       </c>
       <c r="N13" t="n">
-        <v>60.94860424193227</v>
+        <v>60.7032997847335</v>
       </c>
       <c r="O13" t="n">
-        <v>7.806958706303772</v>
+        <v>7.791232237889813</v>
       </c>
       <c r="P13" t="n">
-        <v>397.6691384887971</v>
+        <v>397.727659127396</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26071,28 +26217,28 @@
         <v>0.1021</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5479615900985114</v>
+        <v>0.5451353062539047</v>
       </c>
       <c r="J14" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K14" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2444680130502717</v>
+        <v>0.2450771419203107</v>
       </c>
       <c r="M14" t="n">
-        <v>5.695610310822764</v>
+        <v>5.674908250257888</v>
       </c>
       <c r="N14" t="n">
-        <v>51.21074839193048</v>
+        <v>50.93845397445335</v>
       </c>
       <c r="O14" t="n">
-        <v>7.15616855530461</v>
+        <v>7.137118044032434</v>
       </c>
       <c r="P14" t="n">
-        <v>397.5005024129938</v>
+        <v>397.5301466805753</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26149,28 +26295,28 @@
         <v>0.1046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5303284319303232</v>
+        <v>0.5280075300440634</v>
       </c>
       <c r="J15" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K15" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2012503310002559</v>
+        <v>0.2021000001414686</v>
       </c>
       <c r="M15" t="n">
-        <v>5.771960000594944</v>
+        <v>5.748469203284238</v>
       </c>
       <c r="N15" t="n">
-        <v>61.60188266178473</v>
+        <v>61.24910594758612</v>
       </c>
       <c r="O15" t="n">
-        <v>7.848686683884427</v>
+        <v>7.826180802127314</v>
       </c>
       <c r="P15" t="n">
-        <v>394.3832306126959</v>
+        <v>394.4075820838111</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26227,28 +26373,28 @@
         <v>0.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2871901427106678</v>
+        <v>0.2899238748021512</v>
       </c>
       <c r="J16" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K16" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0620842978167685</v>
+        <v>0.06402943685437801</v>
       </c>
       <c r="M16" t="n">
-        <v>6.040538807653324</v>
+        <v>6.014648482391173</v>
       </c>
       <c r="N16" t="n">
-        <v>68.76242228570156</v>
+        <v>68.37350426107919</v>
       </c>
       <c r="O16" t="n">
-        <v>8.292311034066532</v>
+        <v>8.268827260324114</v>
       </c>
       <c r="P16" t="n">
-        <v>385.8453004358649</v>
+        <v>385.8166187501499</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26305,28 +26451,28 @@
         <v>0.0549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3860186333401942</v>
+        <v>0.3960243181920419</v>
       </c>
       <c r="J17" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K17" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1096575912771246</v>
+        <v>0.1156324942531299</v>
       </c>
       <c r="M17" t="n">
-        <v>6.374747805966182</v>
+        <v>6.384346511392708</v>
       </c>
       <c r="N17" t="n">
-        <v>66.76747782972232</v>
+        <v>66.74734005595715</v>
       </c>
       <c r="O17" t="n">
-        <v>8.17113687498394</v>
+        <v>8.169904531630536</v>
       </c>
       <c r="P17" t="n">
-        <v>364.7243386693597</v>
+        <v>364.6193701205739</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26383,28 +26529,28 @@
         <v>0.1807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4357477480276673</v>
+        <v>-0.4223759007406479</v>
       </c>
       <c r="J18" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K18" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06005766137647028</v>
+        <v>0.05720858842729437</v>
       </c>
       <c r="M18" t="n">
-        <v>7.84278820543279</v>
+        <v>7.816966105948662</v>
       </c>
       <c r="N18" t="n">
-        <v>163.3685619356522</v>
+        <v>163.031543215991</v>
       </c>
       <c r="O18" t="n">
-        <v>12.7815711841562</v>
+        <v>12.76838060272292</v>
       </c>
       <c r="P18" t="n">
-        <v>365.4948580536197</v>
+        <v>365.3549632946575</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26442,7 +26588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S328"/>
+  <dimension ref="A1:S330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58249,6 +58395,200 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-36.04321943623262,174.53210379305003</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-36.043717179931825,174.53275237377048</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-36.04424133408382,174.53335457457635</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-36.04469979282816,174.53397704753678</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-36.04510839317999,174.53468792938963</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-36.04559552098665,174.53538295912352</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-36.0460410131064,174.53609610451838</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-36.04643362062787,174.53682309310685</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-36.046834311676356,174.5375425963944</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-36.047152865291324,174.5383538359103</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-36.04742708886954,174.53917759897493</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-36.047650349037816,174.53995922891426</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-36.047823407398205,174.54072693353504</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-36.04787904360985,174.54149018235088</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-36.04784934507156,174.54223922947193</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>-36.04755031601845,174.54299485021647</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>-36.0472887599051,174.54386412062107</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-36.04321062552841,174.5321156799333</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-36.04370781622774,174.53276499164286</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-36.044243035094325,174.53335243136758</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-36.044692194532665,174.53398418040067</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-36.045106889983714,174.53468915476</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-36.04558927281106,174.53538879434223</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-36.04604484995695,174.5360924165044</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-36.04643197054552,174.53682444739812</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-36.04683446972675,174.5375424896183</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-36.04715066772515,174.53835536426766</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-36.0474294026661,174.53917610130435</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-36.04766706526094,174.53995185279615</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-36.04780248353216,174.5407309953428</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-36.047886401363826,174.5414910479769</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-36.04784492606332,174.54223671668174</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>-36.04755807816224,174.5430015184158</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>-36.0472905465391,174.54386562259714</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
